--- a/error_models/conv_models/nv_32x16_b1_dat-1048576_wt-131072_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x16_b1_dat-1048576_wt-131072_int16/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9899398651119696</v>
+        <v>0.9925454968031818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0100484994525002</v>
+        <v>0.0074450672753588</v>
       </c>
       <c r="I2" t="n">
-        <v>1.15679980802897e-05</v>
+        <v>9.368484009385724e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.6904380412304528</v>
@@ -591,6 +721,84 @@
         <v>3.831134368937746e-06</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.1134651347294479</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.8865348652705521</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -616,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9921321105987853</v>
+        <v>0.9930022262779974</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007855404711135199</v>
+        <v>0.0069873556814015</v>
       </c>
       <c r="I3" t="n">
-        <v>1.24172526296692e-05</v>
+        <v>1.035060315145776e-05</v>
       </c>
       <c r="J3" t="n">
         <v>0.5049396776214951</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0002097320846335</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1134651382990648</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.8865348617009351</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -680,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9981608841760184</v>
+        <v>0.9982967051927618</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0018260543811501</v>
+        <v>0.0016918887358731</v>
       </c>
       <c r="I4" t="n">
-        <v>1.299400538173059e-05</v>
+        <v>1.133863391531114e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.08205414532702961</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6536435774723567</v>
+        <v>0.6536435774723566</v>
       </c>
       <c r="L4" t="n">
         <v>0.0883975738016706</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>1.316741449029808e-06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.999488966231745</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.000511033768255</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.1134655776078659</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.886534422392134</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.99565883700775</v>
+        <v>0.9958126376415908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0043279716726337</v>
+        <v>0.0041757955997687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.312388216656624e-05</v>
+        <v>1.149932119058387e-05</v>
       </c>
       <c r="J5" t="n">
         <v>0.0353119417794963</v>
       </c>
       <c r="K5" t="n">
-        <v>0.654155907243797</v>
+        <v>0.6541559072437971</v>
       </c>
       <c r="L5" t="n">
         <v>0.08732035012190489</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0012773729737253</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9996586954457348</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0003413045542651</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1134654650275489</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.8865345349724512</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -808,13 +1250,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9969466547558516</v>
+        <v>0.9971549139007934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0030403363928147</v>
+        <v>0.0028337287121536</v>
       </c>
       <c r="I6" t="n">
-        <v>1.294141388386699e-05</v>
+        <v>1.128994960318522e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.134396550162023</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0018582032058575</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9994924827563596</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.0005075172436404</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0029927963126168</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.9970072036873832</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9858363176973376</v>
+        <v>0.991722494806804</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0141507197429088</v>
+        <v>0.008266607814090899</v>
       </c>
       <c r="I7" t="n">
-        <v>1.289512230379288e-05</v>
+        <v>1.082994165525338e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0.6814674888472482</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>2.178141238584142e-06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.1134651660305263</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.8865348339694736</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -936,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9927230336736405</v>
+        <v>0.994775491916388</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0072644171262011</v>
+        <v>0.0052140019132471</v>
       </c>
       <c r="I8" t="n">
-        <v>1.248176270861847e-05</v>
+        <v>1.043873291506339e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6389137939065563</v>
+        <v>0.6389137939065564</v>
       </c>
       <c r="K8" t="n">
         <v>0.0843596402157217</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0128381576985811</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.1134700224510219</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.8865299775489779</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1000,16 +1676,16 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9947246418202258</v>
+        <v>0.9977463118159778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0052608597756084</v>
+        <v>0.0022411129236057</v>
       </c>
       <c r="I9" t="n">
-        <v>1.443096671581615e-05</v>
+        <v>1.250782296673644e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5603454636226097</v>
+        <v>0.5603454636226098</v>
       </c>
       <c r="K9" t="n">
         <v>0.163306397514922</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>4.130581467985811e-06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1064,19 +1818,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9984402356972274</v>
+        <v>0.9985898313014954</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0015468839724597</v>
+        <v>0.0013987613816447</v>
       </c>
       <c r="I10" t="n">
-        <v>1.281289286292393e-05</v>
+        <v>1.133987941023924e-05</v>
       </c>
       <c r="J10" t="n">
         <v>0.0578322053702232</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7265606898115738</v>
+        <v>0.726560689811574</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1103,6 +1857,84 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9995052385060484</v>
+        <v>0.9996710425827104</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000481882465442</v>
+        <v>0.0003179295012607</v>
       </c>
       <c r="I11" t="n">
-        <v>1.281159105978328e-05</v>
+        <v>1.096047857889555e-05</v>
       </c>
       <c r="J11" t="n">
         <v>0.0003821344808593</v>
@@ -1149,7 +1981,7 @@
         <v>2.856674776467885e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>8.127367326176515e-06</v>
+        <v>8.127367326176517e-06</v>
       </c>
       <c r="O11" t="n">
         <v>2.562477907320848e-08</v>
@@ -1167,6 +1999,84 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9977391963323496</v>
+        <v>0.9985768428442394</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0022465235414714</v>
+        <v>0.0014105343863879</v>
       </c>
       <c r="I12" t="n">
-        <v>1.421268872910794e-05</v>
+        <v>1.255533192284251e-05</v>
       </c>
       <c r="J12" t="n">
         <v>0.1139639865285054</v>
@@ -1213,13 +2123,13 @@
         <v>0.0219473493631661</v>
       </c>
       <c r="N12" t="n">
-        <v>5.563587955604698e-06</v>
+        <v>5.563587955604697e-06</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5996636389115036</v>
+        <v>0.5996636389115038</v>
       </c>
       <c r="Q12" t="n">
         <v>0.256102387721505</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>1.667611717686357e-05</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9987369300287388</v>
+        <v>0.99954280163552</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0012488833455749</v>
+        <v>0.0004450657111972</v>
       </c>
       <c r="I13" t="n">
-        <v>1.411918823617666e-05</v>
+        <v>1.206521583311442e-05</v>
       </c>
       <c r="J13" t="n">
         <v>0.1946686817202281</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>4.550379459916047e-06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.997846557588731</v>
+        <v>0.9985034692975704</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0021396517428357</v>
+        <v>0.0014842402684826</v>
       </c>
       <c r="I14" t="n">
-        <v>1.372323098350425e-05</v>
+        <v>1.222299649720186e-05</v>
       </c>
       <c r="J14" t="n">
         <v>0.1730093609408536</v>
@@ -1341,7 +2407,7 @@
         <v>0.027509200950554</v>
       </c>
       <c r="N14" t="n">
-        <v>4.45173783709816e-06</v>
+        <v>4.451737837098161e-06</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>1.12642796728715e-05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.998563127471822</v>
+        <v>0.9993927275439672</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0014233229159139</v>
+        <v>0.0005957520345473</v>
       </c>
       <c r="I15" t="n">
-        <v>1.348217481438161e-05</v>
+        <v>1.145298403559502e-05</v>
       </c>
       <c r="J15" t="n">
         <v>0.1897735722557388</v>
@@ -1405,7 +2549,7 @@
         <v>0.0036081241985567</v>
       </c>
       <c r="N15" t="n">
-        <v>6.511259655058769e-06</v>
+        <v>6.511259655058768e-06</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>3.94305410841876e-06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9995692380218532</v>
+        <v>0.9998348845040828</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004176474851512</v>
+        <v>0.0001543126191021</v>
       </c>
       <c r="I16" t="n">
-        <v>1.304705554598571e-05</v>
+        <v>1.073543936528698e-05</v>
       </c>
       <c r="J16" t="n">
         <v>0.000501031994263</v>
@@ -1469,7 +2691,7 @@
         <v>0.0001219881159288</v>
       </c>
       <c r="N16" t="n">
-        <v>9.016744130019723e-06</v>
+        <v>9.016744130019728e-06</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>0.0025318219963179</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9986302994886253</v>
+        <v>0.9989120570099984</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0013554915526824</v>
+        <v>0.0010752802236248</v>
       </c>
       <c r="I17" t="n">
-        <v>1.414152124238756e-05</v>
+        <v>1.259532892685493e-05</v>
       </c>
       <c r="J17" t="n">
         <v>0.059041268483559</v>
@@ -1533,7 +2833,7 @@
         <v>0.0169514479932362</v>
       </c>
       <c r="N17" t="n">
-        <v>8.186167088127765e-06</v>
+        <v>8.186167088127764e-06</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0028367918747943</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.999002335231726</v>
+        <v>0.9996152506167992</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0009843368132886</v>
+        <v>0.0003737074569088</v>
       </c>
       <c r="I18" t="n">
-        <v>1.32605175355829e-05</v>
+        <v>1.097448884196632e-05</v>
       </c>
       <c r="J18" t="n">
         <v>0.1534006865800287</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>1.049621399226641e-05</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9990900071405456</v>
+        <v>0.99925727698579</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0008966960802932</v>
+        <v>0.0007310348778253</v>
       </c>
       <c r="I19" t="n">
-        <v>1.322934171114715e-05</v>
+        <v>1.162069893478356e-05</v>
       </c>
       <c r="J19" t="n">
         <v>0.0023718690402456</v>
@@ -1661,7 +3117,7 @@
         <v>0.003252138836809</v>
       </c>
       <c r="N19" t="n">
-        <v>5.541409231060094e-06</v>
+        <v>5.541409231060093e-06</v>
       </c>
       <c r="O19" t="n">
         <v>6.985923661143657e-09</v>
@@ -1679,6 +3135,84 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9995376417487282</v>
+        <v>0.9997188829638712</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0004499600535325</v>
+        <v>0.0002707949611721</v>
       </c>
       <c r="I20" t="n">
-        <v>1.233076028939667e-05</v>
+        <v>1.025463750688835e-05</v>
       </c>
       <c r="J20" t="n">
         <v>0.0004367158724118</v>
@@ -1743,6 +3277,84 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9988158382932476</v>
+        <v>0.9989977027246644</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0011710471597961</v>
+        <v>0.0009906327941403999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.304710950673765e-05</v>
+        <v>1.159704374527837e-05</v>
       </c>
       <c r="J21" t="n">
         <v>0.0103170096119678</v>
@@ -1789,7 +3401,7 @@
         <v>0.0055550858461062</v>
       </c>
       <c r="N21" t="n">
-        <v>5.718024844229946e-06</v>
+        <v>5.718024844229945e-06</v>
       </c>
       <c r="O21" t="n">
         <v>9.499348101258449e-08</v>
@@ -1807,6 +3419,84 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0912913062438034</v>
+        <v>0.544766203528809</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9086955717154406</v>
+        <v>0.4552220211172726</v>
       </c>
       <c r="I22" t="n">
-        <v>1.305460330616391e-05</v>
+        <v>1.170791646854494e-05</v>
       </c>
       <c r="J22" t="n">
         <v>0.0015318640454454</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9921351622662222</v>
+        <v>0.992135162266222</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1871,6 +3561,84 @@
         <v>1.81138285497559e-07</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0965438148578333</v>
+        <v>0.5403630638925708</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9034428339908028</v>
+        <v>0.4596248713477947</v>
       </c>
       <c r="I23" t="n">
-        <v>1.32837139138249e-05</v>
+        <v>1.199732218463559e-05</v>
       </c>
       <c r="J23" t="n">
         <v>0.0004203344248082</v>
@@ -1914,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.472652267360258e-05</v>
+        <v>5.472652267360259e-05</v>
       </c>
       <c r="N23" t="n">
         <v>6.062964623671276e-08</v>
@@ -1923,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.561965816136525e-08</v>
+        <v>2.561965816136526e-08</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0029857684596269</v>
@@ -1935,6 +3703,84 @@
         <v>1.453077275383628e-06</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1960,16 +3806,16 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.995253352788714</v>
+        <v>0.9963363458474742</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0047328907000086</v>
+        <v>0.0036513169349859</v>
       </c>
       <c r="I24" t="n">
-        <v>1.368907382752359e-05</v>
+        <v>1.226978009003108e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3246839261438227</v>
+        <v>0.3246839261438226</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>0.0006230970049556</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9963279278504596</v>
+        <v>0.9966988271237291</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0036588746244376</v>
+        <v>0.0032893353170395</v>
       </c>
       <c r="I25" t="n">
-        <v>1.313008765303982e-05</v>
+        <v>1.177012178150127e-05</v>
       </c>
       <c r="J25" t="n">
         <v>0.0745932107366061</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0025813003085471</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9978339983451276</v>
+        <v>0.997913328639394</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0021532069063122</v>
+        <v>0.0020754571709255</v>
       </c>
       <c r="I26" t="n">
-        <v>1.272731111034046e-05</v>
+        <v>1.114675223049062e-05</v>
       </c>
       <c r="J26" t="n">
         <v>0.020217616330476</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0051921527713957</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9995047905925106</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.0004952094074893</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.1134654517095715</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.8865345482904285</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9909022354407098</v>
+        <v>0.9923883926478724</v>
       </c>
       <c r="H27" t="n">
-        <v>0.009085301129746899</v>
+        <v>0.007601197261355</v>
       </c>
       <c r="I27" t="n">
-        <v>1.239599209340319e-05</v>
+        <v>1.034265332273575e-05</v>
       </c>
       <c r="J27" t="n">
         <v>0.6032125220626131</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0088485057471944</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.1134653307014169</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.8865346692985832</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9961870556181019</v>
+        <v>0.996645892324768</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0038004701804396</v>
+        <v>0.0033434908133897</v>
       </c>
       <c r="I28" t="n">
-        <v>1.240676400851004e-05</v>
+        <v>1.054942439256518e-05</v>
       </c>
       <c r="J28" t="n">
         <v>0.299515256603349</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0016130576924929</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9992814462561824</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.0007185537438174</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9920657760258718</v>
+        <v>0.9926531260682148</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0079214061303663</v>
+        <v>0.007335899220686</v>
       </c>
       <c r="I29" t="n">
-        <v>1.275040631217258e-05</v>
+        <v>1.090727364950244e-05</v>
       </c>
       <c r="J29" t="n">
         <v>0.4083665308327665</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0067110914684429</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.999663466259394</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.0003365337406058</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0900563826385463</v>
+        <v>0.5438550005551145</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9099303582070142</v>
+        <v>0.4561330997638383</v>
       </c>
       <c r="I30" t="n">
-        <v>1.319171698944348e-05</v>
+        <v>1.183224359738177e-05</v>
       </c>
       <c r="J30" t="n">
         <v>0.0007737488506906</v>
@@ -2383,6 +4697,84 @@
         <v>9.17440937898694e-07</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2408,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.987735482228439</v>
+        <v>0.9920964699419532</v>
       </c>
       <c r="H31" t="n">
-        <v>0.012250805388856</v>
+        <v>0.007891285058573999</v>
       </c>
       <c r="I31" t="n">
-        <v>1.364494525527872e-05</v>
+        <v>1.217756202310258e-05</v>
       </c>
       <c r="J31" t="n">
         <v>0.2518978565546504</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4760072694707405</v>
+        <v>0.4760072694707404</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>1.488829592204132e-05</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.980015560930284</v>
+        <v>0.9841602727068604</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0199703753574743</v>
+        <v>0.0158270487332964</v>
       </c>
       <c r="I32" t="n">
-        <v>1.399627479199893e-05</v>
+        <v>1.261112239334645e-05</v>
       </c>
       <c r="J32" t="n">
         <v>0.1296330535947928</v>
@@ -2493,7 +4963,7 @@
         <v>0.0231117324465718</v>
       </c>
       <c r="N32" t="n">
-        <v>6.061572678110678e-06</v>
+        <v>6.061572678110677e-06</v>
       </c>
       <c r="O32" t="n">
         <v>0.555666083851565</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>0.0041700823196245</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2536,19 +5084,19 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9704344025394236</v>
+        <v>0.9733481108723744</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0295544609994378</v>
+        <v>0.0266429249008851</v>
       </c>
       <c r="I33" t="n">
-        <v>1.106902368899828e-05</v>
+        <v>8.896789290752579e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.2895884993898596</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4380464010271352</v>
+        <v>0.4380464010271353</v>
       </c>
       <c r="L33" t="n">
         <v>6.607166767180572e-07</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.009258005553489899</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1789677798867432</v>
+        <v>0.4357424824515831</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8210202698798891</v>
+        <v>0.5642476670383357</v>
       </c>
       <c r="I34" t="n">
-        <v>1.188279591786986e-05</v>
+        <v>9.783072631523094e-06</v>
       </c>
       <c r="J34" t="n">
         <v>4.186548063593506e-05</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>1.074713733287406e-06</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9877223338292633</v>
+        <v>0.9928900985695481</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0122652866299273</v>
+        <v>0.00709961355920505</v>
       </c>
       <c r="I35" t="n">
-        <v>1.231210335941197e-05</v>
+        <v>1.022043379705872e-05</v>
       </c>
       <c r="J35" t="n">
         <v>0.6814553525006788</v>
@@ -2691,7 +5395,7 @@
         <v>0.04442319611390375</v>
       </c>
       <c r="P35" t="n">
-        <v>2.496663968586958e-06</v>
+        <v>2.496663968586959e-06</v>
       </c>
       <c r="Q35" t="n">
         <v>0.05638150906664545</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>1.079197970508466e-06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.1134652234738602</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.8865347765261398</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9640666049176956</v>
+        <v>0.9708240398214174</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03592113738716531</v>
+        <v>0.02916574091944575</v>
       </c>
       <c r="I36" t="n">
-        <v>1.219025768927034e-05</v>
+        <v>1.015182168708265e-05</v>
       </c>
       <c r="J36" t="n">
         <v>0.6341549629107359</v>
@@ -2755,7 +5537,7 @@
         <v>0.03012469677315775</v>
       </c>
       <c r="P36" t="n">
-        <v>3.491136047877534e-06</v>
+        <v>3.491136047877535e-06</v>
       </c>
       <c r="Q36" t="n">
         <v>0.0107560276790112</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>0.002184122517782174</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.00149625872710345</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.9985037412728965</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2792,13 +5652,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9844394491233111</v>
+        <v>0.9861864841278969</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0155480971762955</v>
+        <v>0.01380304349664465</v>
       </c>
       <c r="I37" t="n">
-        <v>1.238626294349545e-05</v>
+        <v>1.040493800858613e-05</v>
       </c>
       <c r="J37" t="n">
         <v>0.4496885608645576</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0030583748308779</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9888436208969067</v>
+        <v>0.9891940182759165</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01114378986366515</v>
+        <v>0.01079521251553165</v>
       </c>
       <c r="I38" t="n">
-        <v>1.252180197816811e-05</v>
+        <v>1.070177110198303e-05</v>
       </c>
       <c r="J38" t="n">
         <v>0.0836955383739058</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.00244457249583325</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.499831733129697</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.5001682668703029</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9932064032328229</v>
+        <v>0.9935717045086047</v>
       </c>
       <c r="H39" t="n">
-        <v>0.006780174377197676</v>
+        <v>0.0064164527802237</v>
       </c>
       <c r="I39" t="n">
-        <v>1.335495252955324e-05</v>
+        <v>1.177527372179303e-05</v>
       </c>
       <c r="J39" t="n">
         <v>0.04852571673087983</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.003811187751618225</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.7497475996945455</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.00025240030545435</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.085100332450083</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.664899667549917</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9968831779409886</v>
+        <v>0.99705900717756</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0031039466155195</v>
+        <v>0.0029296160469955</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2808006042326e-05</v>
+        <v>1.130933799461535e-05</v>
       </c>
       <c r="J40" t="n">
         <v>0.05375184256480024</v>
@@ -3011,7 +6105,7 @@
         <v>0.03659475358415185</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3348541866356399</v>
+        <v>0.33485418663564</v>
       </c>
       <c r="Q40" t="n">
         <v>8.36417215638921e-05</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.00379759102846425</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.499831733129697</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.0001682668703029</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.0567327530326113</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.4432672469673886</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_32x16_b1_dat-1048576_wt-131072_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x16_b1_dat-1048576_wt-131072_int16/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,312 +425,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9925454968031818</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0074450672753588</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>9.368484009385724e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.6904380412304528</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0364000424894977</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.149756049799321</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0068162200712955</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0332832945412903</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.08319333800303071</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>2.45994516341811e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.0001066537851621</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.562967478688545e-09</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>3.831134368937746e-06</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -742,28 +747,28 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -775,102 +780,108 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.1134651347294479</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>0.8865348652705521</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9930022262779974</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0069873556814015</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1.035060315145776e-05</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.5049396776214951</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.2059805796281625</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.1939670467185183</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0136776831333768</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0404116740130988</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0323267723607774</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>4.045074183755837e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0001571115108401</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>9.568518117512907e-05</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.000148176043974</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0002097320846335</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
@@ -890,22 +901,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -917,114 +928,120 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>0.1134651382990648</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>0.8865348617009351</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9982967051927618</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0016918887358731</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1.133863391531114e-05</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.08205414532702961</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.6536435774723566</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0883975738016706</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0140043190782566</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0884051313218398</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0707179312022737</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>2.503445720441356e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0001262623913025</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0013273064462398</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0013196894703656</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1.316741449029808e-06</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.999488966231745</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.000511033768255</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
       <c r="AA4" t="n">
         <v>1</v>
       </c>
@@ -1032,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1059,114 +1076,120 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0.1134655776078659</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>0.886534422392134</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9958126376415908</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0041757955997687</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1.149932119058387e-05</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.0353119417794963</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.6541559072437971</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.08732035012190489</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0224132494315242</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.1378148266124668</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0507716956094986</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1.903170218727011e-06</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0001250135952502</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0031292251102231</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0004255075474094</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0012773729737253</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.9996586954457348</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.0003413045542651</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
       <c r="AA5" t="n">
         <v>1</v>
       </c>
@@ -1174,22 +1197,22 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1201,114 +1224,120 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.1134654650275489</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>0.8865345349724512</v>
       </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9971549139007934</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0028337287121536</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1.128994960318522e-05</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.134396550162023</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.6003851339677313</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.08082195874815561</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.015392499447724</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.1077670598474071</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0538793583389995</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1.927416548097974e-06</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>8.147852472535597e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0050776964575822</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.0003378685777488</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0018582032058575</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.9994924827563596</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.0005075172436404</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
       <c r="AA6" t="n">
         <v>1</v>
       </c>
@@ -1316,22 +1345,22 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1343,113 +1372,119 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0.0029927963126168</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>0.9970072036873832</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.991722494806804</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.008266607814090899</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1.082994165525338e-05</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.6814674888472482</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0322244257607401</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.07545489885286651</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.0032449356007319</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.1414371769379475</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0471432354165872</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>2.726813613396252e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0190179807864228</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1.22095974589719e-06</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>3.66444540797264e-06</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>2.178141238584142e-06</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
         <v>1</v>
@@ -1458,22 +1493,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1485,113 +1520,119 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>0.1134651660305263</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>0.8865348339694736</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.994775491916388</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0052140019132471</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1.043873291506339e-05</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.6389137939065564</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0843596402157217</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0842708580135379</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.016923541538713</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0902804045704229</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0421291147955742</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>4.350201536820522e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0302321975799732</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.635211787080382e-05</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3.119141980347903e-05</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0128381576985811</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1600,22 +1641,22 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1627,110 +1668,116 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.1134700224510219</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
         <v>0.8865299775489779</v>
       </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9977463118159778</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0022411129236057</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1.250782296673644e-05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.5603454636226098</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.163306397514922</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>3.736824603946146e-07</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.0001544651772559</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>1.064937397840792e-05</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>8.40320537908309e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.2761098438112296</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.457719112164764e-05</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>4.562840212515458e-05</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>4.130581467985811e-06</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1742,22 +1789,22 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1769,22 +1816,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -1793,92 +1840,98 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9985898313014954</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0013987613816447</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1.133987941023924e-05</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0578322053702232</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.726560689811574</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0043269617623941</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>7.481982654969845e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>6.275734400166282e-08</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.2058336406366885</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0054388902416714</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1887,19 +1940,19 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1911,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -1920,13 +1973,13 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -1935,92 +1988,98 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9996710425827104</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0003179295012607</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>1.096047857889555e-05</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0003821344808593</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.9980309515672094</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.856674776467885e-05</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>8.127367326176517e-06</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>2.562477907320848e-08</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0001183623499675</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0014317644246438</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2029,19 +2088,19 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2053,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -2062,13 +2121,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2077,86 +2136,92 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9985768428442394</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0014105343863879</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1.255533192284251e-05</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.1139639865285054</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.0219473493631661</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>5.563587955604697e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.5996636389115038</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.256102387721505</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.271064670937596e-05</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.008267619686028</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1.667611717686357e-05</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2168,22 +2233,22 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2195,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2219,86 +2284,92 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.99954280163552</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0004450657111972</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1.206521583311442e-05</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.1946686817202281</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>7.159319718931638e-05</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>7.252907703485174e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.6664227361971369</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1307103724758139</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>3.01673084535273e-05</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.008084578376564899</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>4.550379459916047e-06</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2310,22 +2381,22 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2337,22 +2408,22 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -2361,86 +2432,92 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9985034692975704</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0014842402684826</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1.222299649720186e-05</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.1730093609408536</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.027509200950554</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>4.451737837098161e-06</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.5239864604000759</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.2673284722754696</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>2.225897704721488e-05</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.008128463001039799</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>1.12642796728715e-05</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2452,22 +2529,22 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2479,22 +2556,22 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -2503,86 +2580,92 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9993927275439672</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0005957520345473</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>1.145298403559502e-05</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.1897735722557388</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0036081241985567</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>6.511259655058768e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.6033007941056634</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1959743780115988</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>3.024043871367887e-05</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0073023692385152</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>3.94305410841876e-06</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2594,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2621,22 +2704,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -2645,86 +2728,92 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9998348845040828</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.0001543126191021</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>1.073543936528698e-05</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.000501031994263</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>5.012398978314556e-05</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>7.104093777006563e-07</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0001219881159288</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>9.016744130019728e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.950395457173402</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.028449407905955</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>4.537230293504468e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0178950019304576</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.0025318219963179</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2736,22 +2825,22 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2763,22 +2852,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -2787,78 +2876,84 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9989120570099984</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0010752802236248</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>1.259532892685493e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.059041268483559</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0046785732544694</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>3.244274765301276e-06</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.0169514479932362</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>8.186167088127764e-06</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.7655340874544992</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.1415545755719473</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0019119677513253</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0074797897368657</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0028367918747943</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
@@ -2878,22 +2973,22 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2905,22 +3000,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -2929,86 +3024,92 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9996152506167992</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0003737074569088</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>1.097448884196632e-05</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.1534006865800287</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>5.293731551644127e-05</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.0036494999826859</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1.018297853022373e-05</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.711610226351956</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.1132917885760481</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.0035940064121943</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.014380108151598</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>1.049621399226641e-05</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3020,22 +3121,22 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3047,22 +3148,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -3071,92 +3172,98 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.99925727698579</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0007310348778253</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>1.162069893478356e-05</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0023718690402456</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.9073999647773427</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.003252138836809</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>5.541409231060093e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>6.985923661143657e-09</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0849734542699499</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0019969572430481</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3165,19 +3272,19 @@
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3189,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
@@ -3198,13 +3305,13 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -3213,92 +3320,98 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9997188829638712</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0002707949611721</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>1.025463750688835e-05</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0004367158724118</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.9662529664443844</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.0032382269176289</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>9.039038885067235e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>2.782141702328953e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0283845413335108</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.0016784151343121</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3307,19 +3420,19 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3331,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -3340,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -3355,92 +3468,98 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9989977027246644</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0009906327941403999</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>1.159704374527837e-05</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0103170096119678</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.892926073974263</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0055550858461062</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>5.718024844229945e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>9.499348101258449e-08</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.08500516441333029</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0061907856985574</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3449,19 +3568,19 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3473,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -3482,13 +3601,13 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -3497,80 +3616,86 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.544766203528809</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.4552220211172726</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>1.170791646854494e-05</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0015318640454454</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.992135162266222</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>4.709720743953189e-06</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>6.21753304043437e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.09535401525899e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0063279422629825</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.81138285497559e-07</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3591,19 +3716,19 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3615,22 +3740,22 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -3639,80 +3764,86 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.5403630638925708</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.4596248713477947</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>1.199732218463559e-05</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.0004203344248082</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9965373822254232</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>5.472652267360259e-05</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>6.062964623671276e-08</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.561965816136526e-08</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0029857684596269</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>1.816034383813531e-07</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>1.453077275383628e-06</v>
       </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3724,28 +3855,28 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3757,22 +3888,22 @@
         <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
         <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -3781,86 +3912,92 @@
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9963363458474742</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0036513169349859</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>1.226978009003108e-05</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.3246839261438226</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0222079492874936</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>4.408691960695651e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.3571733719107337</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.28303860432507</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>3.257893786650822e-05</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0122359962606472</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.0006230970049556</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3872,22 +4009,22 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3899,22 +4036,22 @@
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="n">
         <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -3923,78 +4060,84 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9966988271237291</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0032893353170395</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>1.177012178150127e-05</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.0745932107366061</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0048304204845016</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>2.151898003582641e-06</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0217187318170822</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>7.539356814934609e-06</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.6083809773605994</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.2829918116430394</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0031872180175537</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0017065709398019</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0025813003085471</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -4014,22 +4157,22 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4041,19 +4184,19 @@
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4062,93 +4205,99 @@
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.997913328639394</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0020754571709255</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>1.114675223049062e-05</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.020217616330476</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0037539073198948</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.1196432698349117</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0158697236591494</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0832043383002327</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0332798414364358</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.6975314329034346</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>4.600594473660192e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0017383454886795</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0028848770906337</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0051921527713957</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.9995047905925106</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.0004952094074893</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
       <c r="AA26" t="n">
         <v>1</v>
       </c>
@@ -4156,22 +4305,22 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4183,113 +4332,119 @@
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.1134654517095715</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>0.8865345482904285</v>
       </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9923883926478724</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.007601197261355</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>1.034265332273575e-05</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.6032125220626131</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.1002764052775491</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1055585872220599</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.021254273833134</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.08444209286035199</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.063327242346225</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>3.891879880679359e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.008612447629427899</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.000212974734181</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>2.908386711556607e-05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0088485057471944</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -4298,22 +4453,22 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4325,114 +4480,120 @@
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.1134653307014169</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>0.8865346692985832</v>
       </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.996645892324768</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0033434908133897</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>1.054942439256518e-05</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.299515256603349</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.1463159575460685</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0155864471453264</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0682840914636532</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.048771559827924</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.382560157493341</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.019623850719863</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>9.068781755888557e-06</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0177201279488095</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0016130576924929</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>0.9992814462561824</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.0007185537438174</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
@@ -4440,22 +4601,22 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4467,114 +4628,120 @@
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9926531260682148</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.007335899220686</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>1.090727364950244e-05</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.4083665308327665</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.1679524731093437</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0261730694212701</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0618817591578263</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0441986278842795</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.2796338452151463</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>6.088103133370058e-05</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0020383110565897</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0029831877138908</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0067110914684429</v>
       </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0.999663466259394</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.0003365337406058</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
       <c r="AA29" t="n">
         <v>1</v>
       </c>
@@ -4582,22 +4749,22 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4609,104 +4776,110 @@
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="n">
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.5438550005551145</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.4561330997638383</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>1.183224359738177e-05</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0007737488506906</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9961125930256868</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.835505617171585e-06</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>8.19205988909401e-08</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>5.901760479192478e-09</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0031107499172581</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>9.17440937898694e-07</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -4727,19 +4900,19 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4751,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -4760,13 +4933,13 @@
         <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -4775,86 +4948,92 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9920964699419532</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.007891285058573999</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1.217756202310258e-05</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2518978565546504</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.4760072694707404</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0091332244950628</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>7.212779236865349e-06</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>3.285321532537233e-07</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>5.703672131219749e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.2629110783572917</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.985485737722154e-05</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>2.515547984172077e-06</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>1.488829592204132e-05</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4866,22 +5045,22 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4893,110 +5072,116 @@
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9841602727068604</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0158270487332964</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>1.261112239334645e-05</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.1296330535947928</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.0042605176053427</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.0231117324465718</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>6.061572678110677e-06</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.555666083851565</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>5.190633094486188e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.283107888947277</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.572319592510052e-05</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>2.359839567836147e-05</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.0041700823196245</v>
       </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5008,22 +5193,22 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5035,113 +5220,119 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.9733481108723744</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0266429249008851</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>8.896789290752579e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.2895884993898596</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.4380464010271353</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>6.607166767180572e-07</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0311903087940744</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.0428740409925491</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.1800068084473794</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>2.327769764149273e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.008669843867760599</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.0003570543144421</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>5.715064134781445e-06</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.009258005553489899</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
         <v>1</v>
@@ -5150,22 +5341,22 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -5177,104 +5368,110 @@
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.4357424824515831</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.5642476670383357</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>9.783072631523094e-06</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>4.186548063593506e-05</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.9978820548213924</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>1.559599935899317e-08</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.0003133381710988</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>1.239239014694161e-06</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0017484873823582</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2.265885915724331e-07</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>7.651048659025011e-06</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>3.979521067087211e-06</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>1.074713733287406e-06</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -5295,19 +5492,19 @@
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5319,113 +5516,119 @@
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9928900985695481</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.00709961355920505</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>1.022043379705872e-05</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.6814553525006788</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.04310282555553875</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.0798076707684672</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.003246913967250942</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.09157501601935431</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.04442319611390375</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2.496663968586959e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.05638150906664545</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>6.482886907156661e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>2.953612439561851e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>1.079197970508466e-06</v>
       </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
@@ -5434,22 +5637,22 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5461,137 +5664,143 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
         <v>0.1134652234738602</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
         <v>0.8865347765261398</v>
       </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9708240398214174</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.02916574091944575</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>1.015182168708265e-05</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.6341549629107359</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.0716035639606082</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.1477325222884715</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.02025744177351235</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.08316720345789119</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.03012469677315775</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>3.491136047877535e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.0107560276790112</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>8.867284563044191e-06</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>6.762606965348211e-06</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.002184122517782174</v>
       </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1</v>
-      </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5603,113 +5812,119 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
         <v>0.00149625872710345</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AT36" t="n">
         <v>0.9985037412728965</v>
       </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9861864841278969</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.01380304349664465</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>1.040493800858613e-05</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.4496885608645576</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.2400451000574025</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.1674130936276451</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.0288853308473283</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.05787239030104865</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.0430891256935421</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>4.235000568188841e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.0085826873321092</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.0001425158599632026</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>9.562529314079644e-06</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0030583748308779</v>
       </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -5718,22 +5933,22 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5745,114 +5960,120 @@
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="n">
         <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9891940182759165</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.01079521251553165</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>1.070177110198303e-05</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0836955383739058</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.1145312783323108</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.03043326051776825</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.06546834959728876</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.0613633468868482</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.6246662452819078</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.01099399132682005</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0003961886316841</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.0039574689395451</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.00244457249583325</v>
       </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>0.499831733129697</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.5001682668703029</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
@@ -5860,22 +6081,22 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5887,137 +6108,143 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
         <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9935717045086047</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.0064164527802237</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>1.177527372179303e-05</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.04852571673087983</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2299818821736338</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.0227962804361993</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.01399090011987247</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.071115526733423</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.05185790469331156</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.553063485800277</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>5.981414282230917e-05</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.004538396270346525</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.00025881002133325</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.003811187751618225</v>
       </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
       <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.7497475996945455</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.00025240030545435</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
       <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -6029,137 +6256,143 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AO39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
         <v>0.085100332450083</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>0.664899667549917</v>
       </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.99705900717756</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0029296160469955</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>1.130933799461535e-05</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.05375184256480024</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.455783026722919</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0350647917414635</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.00699377199307935</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.06858243724605641</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.03659475358415185</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.33485418663564</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>8.36417215638921e-05</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00439504488282105</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>9.8760227019e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.00379759102846425</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
       <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>0.499831733129697</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.0001682668703029</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
       <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -6171,30 +6404,36 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AO40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
         <v>0.0567327530326113</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>0.4432672469673886</v>
       </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>0</v>
       </c>
     </row>
